--- a/experiments/completed_experiments/glutamine_202504251440/protocol/mass_spectrometry/ExperimentTemplate.xlsx
+++ b/experiments/completed_experiments/glutamine_202504251440/protocol/mass_spectrometry/ExperimentTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/partially_completed/glutamine_202504251440/protocol/mass_spectrometry/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/completed_experiments/glutamine_202504251440/protocol/mass_spectrometry/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5" documentId="11_A135ED0F83B1D943237533DB6C0660F7A5842258" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4143094-688D-6748-85DE-47A9EC1BB5AB}"/>
